--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260902.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260902.xlsx
@@ -611,56 +611,56 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>135,095</t>
+          <t>136,595</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>27.65%</t>
+          <t>27.53%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>GEV US</t>
+          <t>ORCL US</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>奇異維諾瓦公司</t>
+          <t>甲骨文公司</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>15,425</t>
+          <t>98,940</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>7.67%</t>
+          <t>7.92%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>ORCL US</t>
+          <t>GEV US</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>甲骨文公司</t>
+          <t>奇異維諾瓦公司</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>97,940</t>
+          <t>15,585</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.66%</t>
+          <t>7.89%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>49,815</t>
+          <t>50,365</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.80%</t>
+          <t>5.71%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>118,595</t>
+          <t>119,995</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.45%</t>
+          <t>5.47%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>58,380</t>
+          <t>59,030</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.62%</t>
+          <t>4.43%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.21%</t>
+          <t>3.15%</t>
         </is>
       </c>
     </row>
@@ -765,12 +765,12 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>64,025</t>
+          <t>64,725</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.12%</t>
+          <t>3.14%</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>19,325</t>
+          <t>19,535</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>3.11%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>44,135</t>
+          <t>44,635</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.94%</t>
+          <t>2.95%</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>18,013</t>
+          <t>18,183</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.85%</t>
+          <t>2.72%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>75,305</t>
+          <t>76,135</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.12%</t>
+          <t>2.17%</t>
         </is>
       </c>
     </row>
@@ -875,100 +875,100 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>30,790</t>
+          <t>31,170</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.10%</t>
+          <t>2.11%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>DLR US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>數位不動產信託公司</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>19,785</t>
+          <t>117,970,418</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>2.04%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>D US</t>
+          <t>DLR US</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>道明尼能源公司</t>
+          <t>數位不動產信託公司</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>49,795</t>
+          <t>20,085</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.83%</t>
+          <t>2.03%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>D US</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>道明尼能源公司</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>25,888</t>
+          <t>50,395</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.83%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>XEL US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Xcel 能源</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>35,310</t>
+          <t>26,238</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.54%</t>
         </is>
       </c>
     </row>
@@ -985,34 +985,34 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>19,130</t>
+          <t>19,330</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.52%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>XEL US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>Xcel 能源</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>83,265,568</t>
+          <t>35,760</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.48%</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>58,028</t>
+          <t>58,728</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.41%</t>
+          <t>1.42%</t>
         </is>
       </c>
     </row>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>11,451</t>
+          <t>11,581</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.30%</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>20,908</t>
+          <t>21,138</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1095,56 +1095,56 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>7,790</t>
+          <t>7,890</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.19%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>CRDO US</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Credo科技集團控股有限公司</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>9,436</t>
+          <t>18,205</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.06%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>17,955</t>
+          <t>15,741</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
@@ -1161,34 +1161,34 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>123,925</t>
+          <t>125,285</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>CRDO US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>Credo科技集團控股有限公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>15,571</t>
+          <t>9,536</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
@@ -1205,51 +1205,51 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>19,227</t>
+          <t>19,437</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>PPL Corp</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>36,640</t>
+          <t>42,590</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>PPL Corp</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>42,130</t>
+          <t>37,040</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>11,515</t>
+          <t>11,645</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.70%</t>
+          <t>0.71%</t>
         </is>
       </c>
     </row>
@@ -1293,12 +1293,12 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>582,317</t>
+          <t>607,326</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.33%</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>25,009</t>
+          <t>-231,880</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
